--- a/Reports/FIO/Certificate/Certificate.xlsx
+++ b/Reports/FIO/Certificate/Certificate.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20827"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OpenServer\domains\REPORTS-test\Reports\FIO\Certificate\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F58B793-5DED-4296-A90F-7D6942363706}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="45" windowWidth="28560" windowHeight="12600"/>
+    <workbookView xWindow="120" yWindow="45" windowWidth="28560" windowHeight="12600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -54,9 +60,6 @@
     <t>СПРАВКА</t>
   </si>
   <si>
-    <t>в том, что он (она) действительно зарегистрирован(а) в  г. Белово</t>
-  </si>
-  <si>
     <t>Совместно с ним зарегистрированы:</t>
   </si>
   <si>
@@ -76,13 +79,16 @@
   </si>
   <si>
     <t>$t1['FIO']." ".$t1['birthday']. " г.р. ".$t1['TmpREG']</t>
+  </si>
+  <si>
+    <t>"в том, что он (она) действительно зарегистрирован(а) в  ".$this-&gt;H['pref_region']." " .$this-&gt;H['name_region']</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -205,6 +211,14 @@
       <color rgb="FFFFFFCC"/>
     </mruColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -251,7 +265,7 @@
     </a:clrScheme>
     <a:fontScheme name="Стандартная">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -283,9 +297,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -317,6 +349,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Стандартная">
@@ -492,12 +542,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" customWidth="1"/>
     <col min="2" max="2" width="11" customWidth="1"/>
@@ -513,9 +563,9 @@
     <col min="14" max="16" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="17"/>
@@ -539,19 +589,19 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="17"/>
       <c r="B2" s="17"/>
       <c r="C2" s="17"/>
       <c r="D2" s="15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E2" s="15"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="3"/>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="17"/>
       <c r="B3" s="17"/>
       <c r="C3" s="17"/>
@@ -561,31 +611,31 @@
       <c r="H3" s="2"/>
       <c r="I3" s="3"/>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="17"/>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
       <c r="D4" s="13" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E4" s="13"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="3"/>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="17"/>
       <c r="B5" s="17"/>
       <c r="C5" s="17"/>
       <c r="D5" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E5" s="16"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="3"/>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="17"/>
       <c r="B6" s="17"/>
       <c r="C6" s="17"/>
@@ -595,19 +645,19 @@
       <c r="H6" s="2"/>
       <c r="I6" s="3"/>
     </row>
-    <row r="7" spans="1:16" ht="15" customHeight="1">
+    <row r="7" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="17"/>
       <c r="B7" s="17"/>
       <c r="C7" s="17"/>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="17"/>
       <c r="B8" s="17"/>
       <c r="C8" s="17"/>
     </row>
-    <row r="9" spans="1:16" ht="15" customHeight="1">
+    <row r="9" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
@@ -621,10 +671,10 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:16" s="10" customFormat="1">
+    <row r="10" spans="1:16" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6"/>
       <c r="B10" s="14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C10" s="14"/>
       <c r="D10" s="14"/>
@@ -655,7 +705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -674,46 +724,46 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
     </row>
-    <row r="13" spans="1:16">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
     </row>
-    <row r="14" spans="1:16">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
     </row>
-    <row r="15" spans="1:16">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
     </row>
-    <row r="16" spans="1:16">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="20" spans="11:13">
+    <row r="20" spans="11:13" x14ac:dyDescent="0.25">
       <c r="K20" s="2" t="s">
         <v>6</v>
       </c>
@@ -743,18 +793,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Reports/FIO/Certificate/Certificate.xlsx
+++ b/Reports/FIO/Certificate/Certificate.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OpenServer\domains\REPORTS-test\Reports\FIO\Certificate\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OpenServer\domains\REPORTS\Reports\FIO\Certificate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F58B793-5DED-4296-A90F-7D6942363706}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A31A79CE-AB66-49D8-AF87-C9E89CCCA68A}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="120" yWindow="45" windowWidth="28560" windowHeight="12600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -189,7 +189,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -199,6 +198,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -564,11 +566,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
       <c r="D1" s="11" t="s">
         <v>10</v>
       </c>
@@ -590,55 +592,55 @@
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="15" t="s">
+      <c r="A2" s="16"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="15"/>
+      <c r="E2" s="14"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="3"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
+      <c r="A3" s="16"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
       <c r="D3" s="12"/>
       <c r="E3" s="12"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="3"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="17"/>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="13" t="s">
+    <row r="4" spans="1:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="16"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="13"/>
+      <c r="E4" s="17"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="3"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="17"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
+      <c r="A5" s="16"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
       <c r="D5" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="16"/>
+      <c r="E5" s="15"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="3"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="17"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
+      <c r="A6" s="16"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
       <c r="D6" s="12"/>
       <c r="E6" s="12"/>
       <c r="G6" s="2"/>
@@ -646,14 +648,14 @@
       <c r="I6" s="3"/>
     </row>
     <row r="7" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="17"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
+      <c r="A7" s="16"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="16"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" s="17"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
+      <c r="A8" s="16"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
     </row>
     <row r="9" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
@@ -673,12 +675,12 @@
     </row>
     <row r="10" spans="1:16" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6"/>
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
       <c r="F10" s="7"/>
       <c r="G10" s="8" t="s">
         <v>1</v>

--- a/Reports/FIO/Certificate/Certificate.xlsx
+++ b/Reports/FIO/Certificate/Certificate.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OpenServer\domains\REPORTS\Reports\FIO\Certificate\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OpenServer\domains\REPORTS-test\Reports\FIO\Certificate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A31A79CE-AB66-49D8-AF87-C9E89CCCA68A}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1621F799-A104-4979-9650-3BBBC4331F66}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="120" yWindow="45" windowWidth="28560" windowHeight="12600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,12 +20,12 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Лист1!#REF!</definedName>
   </definedNames>
-  <calcPr calcId="124519" refMode="R1C1"/>
+  <calcPr calcId="124519" calcOnSave="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="21">
   <si>
     <t>t1</t>
   </si>
@@ -82,6 +82,12 @@
   </si>
   <si>
     <t>"в том, что он (она) действительно зарегистрирован(а) в  ".$this-&gt;H['pref_region']." " .$this-&gt;H['name_region']</t>
+  </si>
+  <si>
+    <t>Информация не является исчерпывающей, в связи с всиуплением в силу приказа МВД России</t>
+  </si>
+  <si>
+    <t>№984 от  31.12.2017 г.</t>
   </si>
 </sst>
 </file>
@@ -163,7 +169,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -189,6 +195,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -199,8 +208,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -566,11 +575,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
       <c r="D1" s="11" t="s">
         <v>10</v>
       </c>
@@ -592,21 +601,21 @@
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="16"/>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="14" t="s">
+      <c r="A2" s="17"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="14"/>
+      <c r="E2" s="15"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="3"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="16"/>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
+      <c r="A3" s="17"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
       <c r="D3" s="12"/>
       <c r="E3" s="12"/>
       <c r="G3" s="2"/>
@@ -614,33 +623,33 @@
       <c r="I3" s="3"/>
     </row>
     <row r="4" spans="1:16" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="16"/>
-      <c r="B4" s="16"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="17" t="s">
+      <c r="A4" s="17"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="17"/>
+      <c r="E4" s="13"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="3"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="16"/>
-      <c r="B5" s="16"/>
-      <c r="C5" s="16"/>
+      <c r="A5" s="17"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
       <c r="D5" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="15"/>
+      <c r="E5" s="16"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="3"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="16"/>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
       <c r="D6" s="12"/>
       <c r="E6" s="12"/>
       <c r="G6" s="2"/>
@@ -648,14 +657,14 @@
       <c r="I6" s="3"/>
     </row>
     <row r="7" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="16"/>
-      <c r="B7" s="16"/>
-      <c r="C7" s="16"/>
+      <c r="A7" s="17"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" s="16"/>
-      <c r="B8" s="16"/>
-      <c r="C8" s="16"/>
+      <c r="A8" s="17"/>
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
     </row>
     <row r="9" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
@@ -675,12 +684,12 @@
     </row>
     <row r="10" spans="1:16" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6"/>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
       <c r="F10" s="7"/>
       <c r="G10" s="8" t="s">
         <v>1</v>
@@ -736,15 +745,17 @@
       <c r="E12" s="5"/>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" s="5"/>
+      <c r="A13" s="18" t="s">
+        <v>19</v>
+      </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
-        <v>13</v>
+      <c r="A14" s="18" t="s">
+        <v>20</v>
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -752,14 +763,16 @@
       <c r="E14" s="5"/>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" s="5"/>
+      <c r="A15" s="18"/>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A16" s="5"/>
+      <c r="A16" s="18" t="s">
+        <v>13</v>
+      </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
